--- a/artfynd/A 42501-2022 artfynd.xlsx
+++ b/artfynd/A 42501-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42501-2022 artfynd.xlsx
+++ b/artfynd/A 42501-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104350643</v>
+        <v>104350641</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380007.0928409753</v>
+        <v>380047</v>
       </c>
       <c r="R2" t="n">
-        <v>6742915.911404192</v>
+        <v>6742920</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104350647</v>
+        <v>104350069</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Ömtberget, Vrm</t>
+          <t>N om Ömtbergets NR, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380021.336415169</v>
+        <v>379971</v>
       </c>
       <c r="R3" t="n">
-        <v>6742873.915080181</v>
+        <v>6742910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104350641</v>
+        <v>104350080</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Ömtberget, Vrm</t>
+          <t>N om Ömtbergets NR, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380046.8718677725</v>
+        <v>379997</v>
       </c>
       <c r="R4" t="n">
-        <v>6742920.435697823</v>
+        <v>6742856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,62 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104350646</v>
+        <v>104350083</v>
       </c>
       <c r="B5" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Ömtberget, Vrm</t>
+          <t>N om Ömtbergets NR, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380011.5759789888</v>
+        <v>379988</v>
       </c>
       <c r="R5" t="n">
-        <v>6742860.078228463</v>
+        <v>6742849</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,31 +1051,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104350080</v>
+        <v>104350643</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1159,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N om Ömtbergets NR, Vrm</t>
+          <t>Norr om Ömtberget, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379996.7516280831</v>
+        <v>380007</v>
       </c>
       <c r="R6" t="n">
-        <v>6742855.692087453</v>
+        <v>6742916</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,31 +1148,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104350069</v>
+        <v>104350645</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1271,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N om Ömtbergets NR, Vrm</t>
+          <t>Norr om Ömtberget, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379971.1574388669</v>
+        <v>379953</v>
       </c>
       <c r="R7" t="n">
-        <v>6742909.304532839</v>
+        <v>6742910</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104350645</v>
+        <v>104350646</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379953.0930178231</v>
+        <v>380012</v>
       </c>
       <c r="R8" t="n">
-        <v>6742910.400442448</v>
+        <v>6742860</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104350083</v>
+        <v>104350647</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N om Ömtbergets NR, Vrm</t>
+          <t>Norr om Ömtberget, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>379987.7093710235</v>
+        <v>380022</v>
       </c>
       <c r="R9" t="n">
-        <v>6742848.669359692</v>
+        <v>6742874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,12 +1439,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 42501-2022 artfynd.xlsx
+++ b/artfynd/A 42501-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350641</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350069</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350083</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350643</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350645</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350646</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,8 +1488,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350647</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>